--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="43">
   <si>
     <t>Дата</t>
   </si>
@@ -53,30 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
   </si>
   <si>
     <t>В0843ТМ</t>
@@ -173,8 +149,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -260,11 +237,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -272,9 +250,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -628,20 +606,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46143</v>
       </c>
       <c r="B2">
         <v>1147</v>
       </c>
       <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
         <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" t="s">
-        <v>29</v>
       </c>
       <c r="F2">
         <v>23.687</v>
@@ -659,7 +637,7 @@
         <v>19.66</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -669,20 +647,20 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
+      <c r="A3" s="2">
+        <v>46146</v>
       </c>
       <c r="B3">
         <v>1199</v>
       </c>
       <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
         <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>30</v>
       </c>
       <c r="F3">
         <v>35.908</v>
@@ -700,7 +678,7 @@
         <v>54.58</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -710,20 +688,20 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>15</v>
+      <c r="A4" s="2">
+        <v>46147</v>
       </c>
       <c r="B4">
         <v>1199</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>30.012</v>
@@ -741,7 +719,7 @@
         <v>24.91</v>
       </c>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -751,20 +729,20 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>16</v>
+      <c r="A5" s="2">
+        <v>46149</v>
       </c>
       <c r="B5">
         <v>1147</v>
       </c>
       <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
         <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
       </c>
       <c r="F5">
         <v>27.566</v>
@@ -782,7 +760,7 @@
         <v>22.88</v>
       </c>
       <c r="K5" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -792,20 +770,20 @@
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>17</v>
+      <c r="A6" s="2">
+        <v>46153</v>
       </c>
       <c r="B6">
         <v>1147</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <v>28.867</v>
@@ -823,7 +801,7 @@
         <v>23.96</v>
       </c>
       <c r="K6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -833,20 +811,20 @@
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>18</v>
+      <c r="A7" s="2">
+        <v>46154</v>
       </c>
       <c r="B7">
         <v>1147</v>
       </c>
       <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
         <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
       </c>
       <c r="F7">
         <v>27.537</v>
@@ -864,7 +842,7 @@
         <v>22.58</v>
       </c>
       <c r="K7" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -874,20 +852,20 @@
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>18</v>
+      <c r="A8" s="2">
+        <v>46154</v>
       </c>
       <c r="B8">
         <v>1199</v>
       </c>
       <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>30</v>
       </c>
       <c r="F8">
         <v>24.513</v>
@@ -905,7 +883,7 @@
         <v>37.75</v>
       </c>
       <c r="K8" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -915,20 +893,20 @@
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>19</v>
+      <c r="A9" s="2">
+        <v>46155</v>
       </c>
       <c r="B9">
         <v>1147</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F9">
         <v>4.99</v>
@@ -946,7 +924,7 @@
         <v>10.13</v>
       </c>
       <c r="K9" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -956,20 +934,20 @@
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" t="s">
-        <v>20</v>
+      <c r="A10" s="2">
+        <v>46157</v>
       </c>
       <c r="B10">
         <v>1147</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F10">
         <v>33.375</v>
@@ -987,7 +965,7 @@
         <v>26.7</v>
       </c>
       <c r="K10" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -997,20 +975,20 @@
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" t="s">
-        <v>20</v>
+      <c r="A11" s="2">
+        <v>46157</v>
       </c>
       <c r="B11">
         <v>1147</v>
       </c>
       <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s">
         <v>21</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" t="s">
-        <v>29</v>
       </c>
       <c r="F11">
         <v>33.275</v>
@@ -1028,7 +1006,7 @@
         <v>26.62</v>
       </c>
       <c r="K11" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1038,126 +1016,126 @@
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="6">
+        <v>204.319</v>
+      </c>
+      <c r="C16" s="6">
+        <v>7</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0.8088</v>
+      </c>
+      <c r="E16" s="6">
+        <v>165.26</v>
+      </c>
+      <c r="F16" s="6">
+        <v>167.31</v>
+      </c>
+      <c r="G16" s="6">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="6">
+        <v>60.421</v>
+      </c>
+      <c r="C17" s="6">
+        <v>2</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1.498</v>
+      </c>
+      <c r="E17" s="6">
+        <v>90.51000000000001</v>
+      </c>
+      <c r="F17" s="6">
+        <v>92.33</v>
+      </c>
+      <c r="G17" s="6">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="6">
+        <v>4.99</v>
+      </c>
+      <c r="C18" s="6">
+        <v>1</v>
+      </c>
+      <c r="D18" s="6">
+        <v>2.0301</v>
+      </c>
+      <c r="E18" s="6">
+        <v>10.13</v>
+      </c>
+      <c r="F18" s="6">
+        <v>10.13</v>
+      </c>
+      <c r="G18" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="5">
-        <v>204.319</v>
-      </c>
-      <c r="C16" s="5">
-        <v>7</v>
-      </c>
-      <c r="D16" s="5">
-        <v>0.8088</v>
-      </c>
-      <c r="E16" s="5">
-        <v>165.26</v>
-      </c>
-      <c r="F16" s="5">
-        <v>167.31</v>
-      </c>
-      <c r="G16" s="5">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="5">
-        <v>60.421</v>
-      </c>
-      <c r="C17" s="5">
-        <v>2</v>
-      </c>
-      <c r="D17" s="5">
-        <v>1.498</v>
-      </c>
-      <c r="E17" s="5">
-        <v>90.51000000000001</v>
-      </c>
-      <c r="F17" s="5">
-        <v>92.33</v>
-      </c>
-      <c r="G17" s="5">
-        <v>1.82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="5">
-        <v>4.99</v>
-      </c>
-      <c r="C18" s="5">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5">
-        <v>2.0301</v>
-      </c>
-      <c r="E18" s="5">
-        <v>10.13</v>
-      </c>
-      <c r="F18" s="5">
-        <v>10.13</v>
-      </c>
-      <c r="G18" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="7">
+      <c r="B19" s="8">
         <v>269.73</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <v>10</v>
       </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7">
+      <c r="D19" s="8"/>
+      <c r="E19" s="8">
         <v>265.9</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="8">
         <v>269.77</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="8">
         <v>3.87</v>
       </c>
     </row>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
@@ -182,7 +182,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -192,12 +192,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -248,17 +242,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="27">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,85 +46,37 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
+    <t>Варна Варненчик</t>
+  </si>
+  <si>
+    <t>В5786КН</t>
+  </si>
+  <si>
+    <t>В0843ТМ</t>
   </si>
   <si>
     <t>В8990ВР</t>
   </si>
   <si>
-    <t>В0843ТМ</t>
-  </si>
-  <si>
-    <t>В5786КН</t>
+    <t>78970155027720741</t>
+  </si>
+  <si>
+    <t>78970155027720758</t>
   </si>
   <si>
     <t>78970155027720766</t>
   </si>
   <si>
-    <t>78970155027720758</t>
-  </si>
-  <si>
-    <t>78970155027720741</t>
+    <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
     <t>EKO RACING 100</t>
-  </si>
-  <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>11:07:00</t>
-  </si>
-  <si>
-    <t>14:07:00</t>
-  </si>
-  <si>
-    <t>13:16:00</t>
-  </si>
-  <si>
-    <t>10:12:00</t>
-  </si>
-  <si>
-    <t>14:14:00</t>
-  </si>
-  <si>
-    <t>15:17:00</t>
-  </si>
-  <si>
-    <t>3232140334 3232140334</t>
-  </si>
-  <si>
-    <t>3232154711 3232154711</t>
-  </si>
-  <si>
-    <t>3232203063 3232203063</t>
-  </si>
-  <si>
-    <t>3232466768 3232466768</t>
-  </si>
-  <si>
-    <t>3232471741 3232471741</t>
-  </si>
-  <si>
-    <t>3232543657 3232543657</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА</t>
@@ -547,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -556,17 +505,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -600,327 +546,255 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>39.07</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H2">
+        <v>60.17</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J2">
+        <v>61.34</v>
+      </c>
+      <c r="K2">
+        <v>306860</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46176</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46162</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>19.73</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="H3">
+        <v>14.4</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="J3">
+        <v>14.6</v>
+      </c>
+      <c r="K3">
+        <v>116930</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46176</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.78</v>
+      </c>
+      <c r="H4">
+        <v>17.8</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.82</v>
+      </c>
+      <c r="J4">
+        <v>18.2</v>
+      </c>
+      <c r="K4">
+        <v>115115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>46176</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5">
+        <v>34.1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="H5">
+        <v>24.89</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="J5">
+        <v>25.23</v>
+      </c>
+      <c r="K5">
+        <v>115115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3">
+        <v>46181</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6">
+        <v>28.43</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="H6">
+        <v>20.19</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="J6">
+        <v>20.47</v>
+      </c>
+      <c r="K6">
+        <v>115350</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="3">
+        <v>46184</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E7" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2">
-        <v>31.73</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="F7">
         <v>25</v>
       </c>
-      <c r="H2">
-        <v>0.78</v>
-      </c>
-      <c r="I2" s="1">
-        <v>24.75</v>
-      </c>
-      <c r="J2">
-        <v>0.79</v>
-      </c>
-      <c r="K2" s="1">
-        <v>25.07</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2">
-        <v>114500</v>
-      </c>
-      <c r="N2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46162</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="G7" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J7">
+        <v>17.25</v>
+      </c>
+      <c r="K7">
+        <v>117165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="3">
+        <v>46184</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3">
-        <v>10.03</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3">
-        <v>1.78</v>
-      </c>
-      <c r="I3" s="1">
-        <v>17.85</v>
-      </c>
-      <c r="J3">
-        <v>1.82</v>
-      </c>
-      <c r="K3" s="1">
-        <v>18.25</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3">
-        <v>114500</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46162</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4">
-        <v>26.59</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4">
-        <v>0.78</v>
-      </c>
-      <c r="I4" s="1">
-        <v>20.74</v>
-      </c>
-      <c r="J4">
-        <v>0.79</v>
-      </c>
-      <c r="K4" s="1">
-        <v>21.01</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4">
-        <v>116605</v>
-      </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46163</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="F8">
+        <v>22.7</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="H8">
+        <v>15.44</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J8">
+        <v>15.66</v>
+      </c>
+      <c r="K8">
+        <v>115550</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5">
-        <v>36.91</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5">
-        <v>1.54</v>
-      </c>
-      <c r="I5" s="1">
-        <v>56.84</v>
-      </c>
-      <c r="J5">
-        <v>1.57</v>
-      </c>
-      <c r="K5" s="1">
-        <v>57.95</v>
-      </c>
-      <c r="L5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5">
-        <v>306715</v>
-      </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="3">
-        <v>46169</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>32.52</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6">
-        <v>0.76</v>
-      </c>
-      <c r="I6" s="1">
-        <v>24.72</v>
-      </c>
-      <c r="J6">
-        <v>0.77</v>
-      </c>
-      <c r="K6" s="1">
-        <v>25.04</v>
-      </c>
-      <c r="L6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6">
-        <v>116800</v>
-      </c>
-      <c r="N6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="3">
-        <v>46169</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>30.22</v>
-      </c>
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7">
-        <v>0.76</v>
-      </c>
-      <c r="I7" s="1">
-        <v>22.97</v>
-      </c>
-      <c r="J7">
-        <v>0.77</v>
-      </c>
-      <c r="K7" s="1">
-        <v>23.27</v>
-      </c>
-      <c r="L7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7">
-        <v>114730</v>
-      </c>
-      <c r="N7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="3">
-        <v>46171</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8">
-        <v>13.2</v>
-      </c>
-      <c r="G8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8">
-        <v>0.76</v>
-      </c>
-      <c r="I8" s="1">
-        <v>10.03</v>
-      </c>
-      <c r="J8">
-        <v>0.77</v>
-      </c>
-      <c r="K8" s="1">
-        <v>10.16</v>
-      </c>
-      <c r="L8" t="s">
-        <v>31</v>
-      </c>
-      <c r="M8">
-        <v>114860</v>
-      </c>
-      <c r="N8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -928,102 +802,102 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:11">
       <c r="A12" s="5" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B13" s="7">
-        <v>134.26</v>
+        <v>129.96</v>
       </c>
       <c r="C13" s="7">
         <v>5</v>
       </c>
       <c r="D13" s="8">
-        <v>0.7687</v>
+        <v>0.7073</v>
       </c>
       <c r="E13" s="7">
-        <v>103.21</v>
+        <v>91.92</v>
       </c>
       <c r="F13" s="7">
-        <v>104.55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>93.20999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B14" s="7">
-        <v>36.91</v>
+        <v>39.07</v>
       </c>
       <c r="C14" s="7">
         <v>1</v>
       </c>
       <c r="D14" s="8">
-        <v>1.54</v>
+        <v>1.5401</v>
       </c>
       <c r="E14" s="7">
-        <v>56.84</v>
+        <v>60.17</v>
       </c>
       <c r="F14" s="7">
-        <v>57.95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>61.34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B15" s="7">
-        <v>10.03</v>
+        <v>10</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
       </c>
       <c r="D15" s="8">
-        <v>1.7797</v>
+        <v>1.78</v>
       </c>
       <c r="E15" s="7">
-        <v>17.85</v>
+        <v>17.8</v>
       </c>
       <c r="F15" s="7">
-        <v>18.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B16" s="10">
-        <v>181.2</v>
+        <v>179.03</v>
       </c>
       <c r="C16" s="10">
         <v>7</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="10">
-        <v>177.9</v>
+        <v>169.89</v>
       </c>
       <c r="F16" s="10">
-        <v>180.75</v>
+        <v>172.75</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="35">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Варненчик</t>
   </si>
   <si>
@@ -77,6 +83,24 @@
   </si>
   <si>
     <t>EKO RACING 100</t>
+  </si>
+  <si>
+    <t>11:33</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>07:19</t>
+  </si>
+  <si>
+    <t>11:47</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА</t>
@@ -496,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -509,10 +533,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -546,22 +572,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46175</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>39.07</v>
@@ -578,25 +610,31 @@
       <c r="J2">
         <v>61.34</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2">
         <v>306860</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>191395</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46176</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>19.73</v>
@@ -613,25 +651,31 @@
       <c r="J3">
         <v>14.6</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3">
         <v>116930</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>192127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46176</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4">
         <v>10</v>
@@ -648,25 +692,31 @@
       <c r="J4">
         <v>18.2</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4">
         <v>115115</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="M4">
+        <v>192200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46176</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F5">
         <v>34.1</v>
@@ -683,25 +733,31 @@
       <c r="J5">
         <v>25.23</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5">
         <v>115115</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="M5">
+        <v>192200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46181</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <v>28.43</v>
@@ -718,25 +774,31 @@
       <c r="J6">
         <v>20.47</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6">
         <v>115350</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="M6">
+        <v>113508</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46184</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>25</v>
@@ -753,25 +815,31 @@
       <c r="J7">
         <v>17.25</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7">
         <v>117165</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="M7">
+        <v>113765</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46184</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F8">
         <v>22.7</v>
@@ -788,13 +856,19 @@
       <c r="J8">
         <v>15.66</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8">
         <v>115550</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="M8">
+        <v>197422</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="4" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -802,18 +876,18 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:13">
       <c r="A12" s="5" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>7</v>
@@ -822,9 +896,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:13">
       <c r="A13" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B13" s="7">
         <v>129.96</v>
@@ -842,9 +916,9 @@
         <v>93.20999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:13">
       <c r="A14" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B14" s="7">
         <v>39.07</v>
@@ -862,9 +936,9 @@
         <v>61.34</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:13">
       <c r="A15" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B15" s="7">
         <v>10</v>
@@ -882,9 +956,9 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:13">
       <c r="A16" s="9" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B16" s="10">
         <v>179.03</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="34">
   <si>
     <t>Дата</t>
   </si>
@@ -49,10 +49,7 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
+    <t>Варна</t>
   </si>
   <si>
     <t>Варна Варненчик</t>
@@ -82,25 +79,25 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>EKO RACING 100</t>
-  </si>
-  <si>
-    <t>11:33</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>07:19</t>
-  </si>
-  <si>
-    <t>11:47</t>
+    <t>2026-06-16 11:53:51</t>
+  </si>
+  <si>
+    <t>2026-06-16 14:56:50</t>
+  </si>
+  <si>
+    <t>2026-06-16 15:37:20</t>
+  </si>
+  <si>
+    <t>2026-06-19 13:56:24</t>
+  </si>
+  <si>
+    <t>2026-06-22 14:41:30</t>
+  </si>
+  <si>
+    <t>2026-06-24 10:23:23</t>
+  </si>
+  <si>
+    <t>2026-06-24 12:40:10</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА</t>
@@ -520,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -533,12 +530,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -572,303 +567,255 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46189</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>21.48</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H2">
+        <v>32.86</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J2">
+        <v>33.51</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46189</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46175</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>37.48</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H3">
+        <v>24.74</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J3">
+        <v>25.11</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46189</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>31.08</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H4">
+        <v>20.51</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J4">
+        <v>20.82</v>
+      </c>
+      <c r="K4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5">
+        <v>13.36</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H5">
+        <v>8.68</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J5">
+        <v>8.82</v>
+      </c>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3">
+        <v>46195</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6">
+        <v>28.67</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H6">
+        <v>18.64</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J6">
+        <v>18.92</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>42.63</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H7">
+        <v>63.09</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J7">
+        <v>64.37</v>
+      </c>
+      <c r="K7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D8" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E8" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
-        <v>39.07</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="H2">
-        <v>60.17</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="J2">
-        <v>61.34</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2">
-        <v>306860</v>
-      </c>
-      <c r="M2">
-        <v>191395</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46176</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>19.73</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.73</v>
-      </c>
-      <c r="H3">
-        <v>14.4</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0.74</v>
-      </c>
-      <c r="J3">
-        <v>14.6</v>
-      </c>
-      <c r="K3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3">
-        <v>116930</v>
-      </c>
-      <c r="M3">
-        <v>192127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46176</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4">
-        <v>10</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="H4">
-        <v>17.8</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="J4">
-        <v>18.2</v>
-      </c>
-      <c r="K4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4">
-        <v>115115</v>
-      </c>
-      <c r="M4">
-        <v>192200</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3">
-        <v>46176</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>34.1</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.73</v>
-      </c>
-      <c r="H5">
-        <v>24.89</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0.74</v>
-      </c>
-      <c r="J5">
-        <v>25.23</v>
-      </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5">
-        <v>115115</v>
-      </c>
-      <c r="M5">
-        <v>192200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="3">
-        <v>46181</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6">
-        <v>28.43</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="H6">
-        <v>20.19</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0.72</v>
-      </c>
-      <c r="J6">
-        <v>20.47</v>
-      </c>
-      <c r="K6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6">
-        <v>115350</v>
-      </c>
-      <c r="M6">
-        <v>113508</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="3">
-        <v>46184</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7">
-        <v>25</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="H7">
-        <v>17</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="J7">
-        <v>17.25</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="F8">
+        <v>25.35</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H8">
+        <v>16.48</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J8">
+        <v>16.73</v>
+      </c>
+      <c r="K8" t="s">
         <v>27</v>
       </c>
-      <c r="L7">
-        <v>117165</v>
-      </c>
-      <c r="M7">
-        <v>113765</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="3">
-        <v>46184</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8">
-        <v>22.7</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="H8">
-        <v>15.44</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="J8">
-        <v>15.66</v>
-      </c>
-      <c r="K8" t="s">
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="L8">
-        <v>115550</v>
-      </c>
-      <c r="M8">
-        <v>197422</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="4" t="s">
-        <v>29</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -876,18 +823,18 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:11">
       <c r="A12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>33</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>7</v>
@@ -896,82 +843,62 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:11">
       <c r="A13" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="7">
-        <v>129.96</v>
+        <v>135.94</v>
       </c>
       <c r="C13" s="7">
         <v>5</v>
       </c>
       <c r="D13" s="8">
-        <v>0.7073</v>
+        <v>0.6551</v>
       </c>
       <c r="E13" s="7">
-        <v>91.92</v>
+        <v>89.05</v>
       </c>
       <c r="F13" s="7">
-        <v>93.20999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>90.40000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="7">
-        <v>39.07</v>
+        <v>64.11</v>
       </c>
       <c r="C14" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="8">
-        <v>1.5401</v>
+        <v>1.4966</v>
       </c>
       <c r="E14" s="7">
-        <v>60.17</v>
+        <v>95.95</v>
       </c>
       <c r="F14" s="7">
-        <v>61.34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="7">
-        <v>10</v>
-      </c>
-      <c r="C15" s="7">
-        <v>1</v>
-      </c>
-      <c r="D15" s="8">
-        <v>1.78</v>
-      </c>
-      <c r="E15" s="7">
-        <v>17.8</v>
-      </c>
-      <c r="F15" s="7">
-        <v>18.2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="10">
-        <v>179.03</v>
-      </c>
-      <c r="C16" s="10">
+        <v>97.88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="10">
+        <v>200.05</v>
+      </c>
+      <c r="C15" s="10">
         <v>7</v>
       </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="10">
-        <v>169.89</v>
-      </c>
-      <c r="F16" s="10">
-        <v>172.75</v>
+      <c r="D15" s="8"/>
+      <c r="E15" s="10">
+        <v>185</v>
+      </c>
+      <c r="F15" s="10">
+        <v>188.28</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="51">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,55 +52,103 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>В0843ТМ</t>
+  </si>
+  <si>
+    <t>В8990ВР</t>
   </si>
   <si>
     <t>В5786КН</t>
   </si>
   <si>
-    <t>В0843ТМ</t>
-  </si>
-  <si>
-    <t>В8990ВР</t>
+    <t>78970155027720758</t>
+  </si>
+  <si>
+    <t>78970155027720766</t>
   </si>
   <si>
     <t>78970155027720741</t>
   </si>
   <si>
-    <t>78970155027720758</t>
-  </si>
-  <si>
-    <t>78970155027720766</t>
+    <t>E GAS LPG</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>2026-06-16 11:53:51</t>
-  </si>
-  <si>
-    <t>2026-06-16 14:56:50</t>
-  </si>
-  <si>
-    <t>2026-06-16 15:37:20</t>
-  </si>
-  <si>
-    <t>2026-06-19 13:56:24</t>
-  </si>
-  <si>
-    <t>2026-06-22 14:41:30</t>
-  </si>
-  <si>
-    <t>2026-06-24 10:23:23</t>
-  </si>
-  <si>
-    <t>2026-06-24 12:40:10</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>14:57:00</t>
+  </si>
+  <si>
+    <t>15:37:00</t>
+  </si>
+  <si>
+    <t>11:53:00</t>
+  </si>
+  <si>
+    <t>13:56:00</t>
+  </si>
+  <si>
+    <t>14:41:00</t>
+  </si>
+  <si>
+    <t>10:23:00</t>
+  </si>
+  <si>
+    <t>12:40:00</t>
+  </si>
+  <si>
+    <t>10:39:00</t>
+  </si>
+  <si>
+    <t>21:54:00</t>
+  </si>
+  <si>
+    <t>13:55:00</t>
+  </si>
+  <si>
+    <t>3233422581 3233422581</t>
+  </si>
+  <si>
+    <t>3233438645 3233438645</t>
+  </si>
+  <si>
+    <t>3233444849 3233444849</t>
+  </si>
+  <si>
+    <t>3233576746 3233576746</t>
+  </si>
+  <si>
+    <t>3233695723 3233695723</t>
+  </si>
+  <si>
+    <t>3233805247 3233805247</t>
+  </si>
+  <si>
+    <t>3233806162 3233806162</t>
+  </si>
+  <si>
+    <t>3233953100 3233953100</t>
+  </si>
+  <si>
+    <t>3234067920 3234067920</t>
+  </si>
+  <si>
+    <t>3234098555 3234098555</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА</t>
@@ -517,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -526,14 +577,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -567,343 +621,547 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>21.48</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.53</v>
+        <v>37.48</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
       </c>
       <c r="H2">
-        <v>32.86</v>
+        <v>0.66</v>
       </c>
       <c r="I2" s="1">
-        <v>1.56</v>
+        <v>24.74</v>
       </c>
       <c r="J2">
-        <v>33.51</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>0.67</v>
+      </c>
+      <c r="K2" s="1">
+        <v>25.11</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2">
+        <v>117320</v>
+      </c>
+      <c r="N2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46189</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>37.48</v>
-      </c>
-      <c r="G3" s="1">
+        <v>31.07</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3">
         <v>0.66</v>
       </c>
-      <c r="H3">
-        <v>24.74</v>
-      </c>
       <c r="I3" s="1">
+        <v>20.51</v>
+      </c>
+      <c r="J3">
         <v>0.67</v>
       </c>
-      <c r="J3">
-        <v>25.11</v>
-      </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="K3" s="1">
+        <v>20.82</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3">
+        <v>115760</v>
+      </c>
+      <c r="N3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46189</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>31.08</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.66</v>
+        <v>21.48</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
       </c>
       <c r="H4">
-        <v>20.51</v>
+        <v>1.53</v>
       </c>
       <c r="I4" s="1">
-        <v>0.67</v>
+        <v>32.86</v>
       </c>
       <c r="J4">
-        <v>20.82</v>
-      </c>
-      <c r="K4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>1.56</v>
+      </c>
+      <c r="K4" s="1">
+        <v>33.51</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4">
+        <v>307113</v>
+      </c>
+      <c r="N4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46192</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5">
         <v>13.36</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5">
         <v>0.65</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>8.68</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>0.66</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>8.82</v>
       </c>
-      <c r="K5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5">
+        <v>115920</v>
+      </c>
+      <c r="N5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46195</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6">
         <v>28.67</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6">
         <v>0.65</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>18.64</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>0.66</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>18.92</v>
       </c>
-      <c r="K6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6">
+        <v>117520</v>
+      </c>
+      <c r="N6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46197</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F7">
         <v>42.63</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7">
         <v>1.48</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>63.09</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.51</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>64.37</v>
       </c>
-      <c r="K7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7">
+        <v>307370</v>
+      </c>
+      <c r="N7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46197</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F8">
         <v>25.35</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8">
         <v>0.65</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>16.48</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>0.66</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>16.73</v>
       </c>
-      <c r="K8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="L8" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="M8">
+        <v>114700</v>
+      </c>
+      <c r="N8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9">
+        <v>28.88</v>
+      </c>
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9">
+        <v>0.65</v>
+      </c>
+      <c r="I9" s="1">
+        <v>18.77</v>
+      </c>
+      <c r="J9">
+        <v>0.66</v>
+      </c>
+      <c r="K9" s="1">
+        <v>19.06</v>
+      </c>
+      <c r="L9" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="6" t="s">
+      <c r="M9">
+        <v>116120</v>
+      </c>
+      <c r="N9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10">
+        <v>37.08</v>
+      </c>
+      <c r="G10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10">
+        <v>0.65</v>
+      </c>
+      <c r="I10" s="1">
+        <v>24.1</v>
+      </c>
+      <c r="J10">
+        <v>0.66</v>
+      </c>
+      <c r="K10" s="1">
+        <v>24.47</v>
+      </c>
+      <c r="L10" t="s">
+        <v>33</v>
+      </c>
+      <c r="M10">
+        <v>117940</v>
+      </c>
+      <c r="N10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="7">
-        <v>135.94</v>
-      </c>
-      <c r="C13" s="7">
-        <v>5</v>
-      </c>
-      <c r="D13" s="8">
-        <v>0.6551</v>
-      </c>
-      <c r="E13" s="7">
-        <v>89.05</v>
-      </c>
-      <c r="F13" s="7">
-        <v>90.40000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="7">
+      <c r="E11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11">
+        <v>26.77</v>
+      </c>
+      <c r="G11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11">
+        <v>0.65</v>
+      </c>
+      <c r="I11" s="1">
+        <v>17.4</v>
+      </c>
+      <c r="J11">
+        <v>0.66</v>
+      </c>
+      <c r="K11" s="1">
+        <v>17.67</v>
+      </c>
+      <c r="L11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M11">
+        <v>116250</v>
+      </c>
+      <c r="N11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="7">
+        <v>228.66</v>
+      </c>
+      <c r="C16" s="7">
+        <v>8</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0.653</v>
+      </c>
+      <c r="E16" s="7">
+        <v>149.32</v>
+      </c>
+      <c r="F16" s="7">
+        <v>151.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="7">
         <v>64.11</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C17" s="7">
         <v>2</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D17" s="8">
         <v>1.4966</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E17" s="7">
         <v>95.95</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F17" s="7">
         <v>97.88</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="10">
-        <v>200.05</v>
-      </c>
-      <c r="C15" s="10">
-        <v>7</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="10">
-        <v>185</v>
-      </c>
-      <c r="F15" s="10">
-        <v>188.28</v>
+    <row r="18" spans="1:6">
+      <c r="A18" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="10">
+        <v>292.77</v>
+      </c>
+      <c r="C18" s="10">
+        <v>10</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="10">
+        <v>245.27</v>
+      </c>
+      <c r="F18" s="10">
+        <v>249.48</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A14:F14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="39">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,10 +55,13 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1147 Варна Ситроен</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>Варна Варненчик</t>
+  </si>
+  <si>
+    <t>В5786КН</t>
   </si>
   <si>
     <t>В0843ТМ</t>
@@ -70,7 +70,7 @@
     <t>В8990ВР</t>
   </si>
   <si>
-    <t>В5786КН</t>
+    <t>78970155027720741</t>
   </si>
   <si>
     <t>78970155027720758</t>
@@ -79,76 +79,40 @@
     <t>78970155027720766</t>
   </si>
   <si>
-    <t>78970155027720741</t>
+    <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>14:57:00</t>
-  </si>
-  <si>
-    <t>15:37:00</t>
-  </si>
-  <si>
-    <t>11:53:00</t>
-  </si>
-  <si>
-    <t>13:56:00</t>
-  </si>
-  <si>
-    <t>14:41:00</t>
-  </si>
-  <si>
-    <t>10:23:00</t>
-  </si>
-  <si>
-    <t>12:40:00</t>
-  </si>
-  <si>
-    <t>10:39:00</t>
-  </si>
-  <si>
-    <t>21:54:00</t>
-  </si>
-  <si>
-    <t>13:55:00</t>
-  </si>
-  <si>
-    <t>3233422581 3233422581</t>
-  </si>
-  <si>
-    <t>3233438645 3233438645</t>
-  </si>
-  <si>
-    <t>3233444849 3233444849</t>
-  </si>
-  <si>
-    <t>3233576746 3233576746</t>
-  </si>
-  <si>
-    <t>3233695723 3233695723</t>
-  </si>
-  <si>
-    <t>3233805247 3233805247</t>
-  </si>
-  <si>
-    <t>3233806162 3233806162</t>
-  </si>
-  <si>
-    <t>3233953100 3233953100</t>
-  </si>
-  <si>
-    <t>3234067920 3234067920</t>
-  </si>
-  <si>
-    <t>3234098555 3234098555</t>
+    <t>11:54</t>
+  </si>
+  <si>
+    <t>14:56</t>
+  </si>
+  <si>
+    <t>15:37</t>
+  </si>
+  <si>
+    <t>13:56</t>
+  </si>
+  <si>
+    <t>14:41</t>
+  </si>
+  <si>
+    <t>10:23</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>10:39</t>
+  </si>
+  <si>
+    <t>21:54</t>
+  </si>
+  <si>
+    <t>13:55</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА</t>
@@ -568,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -577,17 +541,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -627,55 +590,49 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>37.48</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
+        <v>21.48</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.53</v>
       </c>
       <c r="H2">
-        <v>0.66</v>
+        <v>32.86</v>
       </c>
       <c r="I2" s="1">
-        <v>24.74</v>
+        <v>1.56</v>
       </c>
       <c r="J2">
-        <v>0.67</v>
-      </c>
-      <c r="K2" s="1">
-        <v>25.11</v>
-      </c>
-      <c r="L2" t="s">
-        <v>25</v>
+        <v>33.51</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2">
+        <v>307113</v>
       </c>
       <c r="M2">
-        <v>117320</v>
-      </c>
-      <c r="N2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>275702</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46189</v>
       </c>
@@ -683,87 +640,81 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
         <v>22</v>
       </c>
       <c r="F3">
-        <v>31.07</v>
-      </c>
-      <c r="G3" t="s">
+        <v>37.48</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H3">
+        <v>24.74</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J3">
+        <v>25.11</v>
+      </c>
+      <c r="K3" t="s">
         <v>24</v>
       </c>
-      <c r="H3">
-        <v>0.66</v>
-      </c>
-      <c r="I3" s="1">
-        <v>20.51</v>
-      </c>
-      <c r="J3">
-        <v>0.67</v>
-      </c>
-      <c r="K3" s="1">
-        <v>20.82</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
+      <c r="L3">
+        <v>117320</v>
       </c>
       <c r="M3">
-        <v>115760</v>
-      </c>
-      <c r="N3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>200295</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46189</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>21.48</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
+        <v>31.08</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.66</v>
       </c>
       <c r="H4">
-        <v>1.53</v>
+        <v>20.51</v>
       </c>
       <c r="I4" s="1">
-        <v>32.86</v>
+        <v>0.67</v>
       </c>
       <c r="J4">
-        <v>1.56</v>
-      </c>
-      <c r="K4" s="1">
-        <v>33.51</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
+        <v>20.82</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4">
+        <v>115760</v>
       </c>
       <c r="M4">
-        <v>307113</v>
-      </c>
-      <c r="N4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>200307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46192</v>
       </c>
@@ -782,32 +733,29 @@
       <c r="F5">
         <v>13.36</v>
       </c>
-      <c r="G5" t="s">
-        <v>24</v>
+      <c r="G5" s="1">
+        <v>0.65</v>
       </c>
       <c r="H5">
-        <v>0.65</v>
+        <v>8.68</v>
       </c>
       <c r="I5" s="1">
-        <v>8.68</v>
+        <v>0.66</v>
       </c>
       <c r="J5">
-        <v>0.66</v>
-      </c>
-      <c r="K5" s="1">
         <v>8.82</v>
       </c>
-      <c r="L5" t="s">
-        <v>28</v>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5">
+        <v>115920</v>
       </c>
       <c r="M5">
-        <v>115920</v>
-      </c>
-      <c r="N5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>116805</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46195</v>
       </c>
@@ -826,32 +774,29 @@
       <c r="F6">
         <v>28.67</v>
       </c>
-      <c r="G6" t="s">
-        <v>24</v>
+      <c r="G6" s="1">
+        <v>0.65</v>
       </c>
       <c r="H6">
-        <v>0.65</v>
+        <v>18.64</v>
       </c>
       <c r="I6" s="1">
-        <v>18.64</v>
+        <v>0.66</v>
       </c>
       <c r="J6">
-        <v>0.66</v>
-      </c>
-      <c r="K6" s="1">
         <v>18.92</v>
       </c>
-      <c r="L6" t="s">
-        <v>29</v>
+      <c r="K6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6">
+        <v>117520</v>
       </c>
       <c r="M6">
-        <v>117520</v>
-      </c>
-      <c r="N6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>203524</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46197</v>
       </c>
@@ -859,43 +804,40 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>21</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
       </c>
       <c r="F7">
         <v>42.63</v>
       </c>
-      <c r="G7" t="s">
-        <v>24</v>
+      <c r="G7" s="1">
+        <v>1.48</v>
       </c>
       <c r="H7">
-        <v>1.48</v>
+        <v>63.09</v>
       </c>
       <c r="I7" s="1">
-        <v>63.09</v>
+        <v>1.51</v>
       </c>
       <c r="J7">
-        <v>1.51</v>
-      </c>
-      <c r="K7" s="1">
         <v>64.37</v>
       </c>
-      <c r="L7" t="s">
-        <v>30</v>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7">
+        <v>307370</v>
       </c>
       <c r="M7">
-        <v>307370</v>
-      </c>
-      <c r="N7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>204421</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46197</v>
       </c>
@@ -914,37 +856,34 @@
       <c r="F8">
         <v>25.35</v>
       </c>
-      <c r="G8" t="s">
-        <v>24</v>
+      <c r="G8" s="1">
+        <v>0.65</v>
       </c>
       <c r="H8">
-        <v>0.65</v>
+        <v>16.48</v>
       </c>
       <c r="I8" s="1">
-        <v>16.48</v>
+        <v>0.66</v>
       </c>
       <c r="J8">
-        <v>0.66</v>
-      </c>
-      <c r="K8" s="1">
         <v>16.73</v>
       </c>
-      <c r="L8" t="s">
-        <v>31</v>
+      <c r="K8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8">
+        <v>114700</v>
       </c>
       <c r="M8">
-        <v>114700</v>
-      </c>
-      <c r="N8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>204506</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="3">
         <v>46199</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -958,32 +897,29 @@
       <c r="F9">
         <v>28.88</v>
       </c>
-      <c r="G9" t="s">
-        <v>24</v>
+      <c r="G9" s="1">
+        <v>0.65</v>
       </c>
       <c r="H9">
-        <v>0.65</v>
+        <v>18.77</v>
       </c>
       <c r="I9" s="1">
-        <v>18.77</v>
+        <v>0.66</v>
       </c>
       <c r="J9">
-        <v>0.66</v>
-      </c>
-      <c r="K9" s="1">
         <v>19.06</v>
       </c>
-      <c r="L9" t="s">
-        <v>32</v>
+      <c r="K9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9">
+        <v>116120</v>
       </c>
       <c r="M9">
-        <v>116120</v>
-      </c>
-      <c r="N9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>278518</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="3">
         <v>46202</v>
       </c>
@@ -1002,32 +938,29 @@
       <c r="F10">
         <v>37.08</v>
       </c>
-      <c r="G10" t="s">
-        <v>24</v>
+      <c r="G10" s="1">
+        <v>0.65</v>
       </c>
       <c r="H10">
-        <v>0.65</v>
+        <v>24.1</v>
       </c>
       <c r="I10" s="1">
-        <v>24.1</v>
+        <v>0.66</v>
       </c>
       <c r="J10">
-        <v>0.66</v>
-      </c>
-      <c r="K10" s="1">
         <v>24.47</v>
       </c>
-      <c r="L10" t="s">
-        <v>33</v>
+      <c r="K10" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10">
+        <v>117940</v>
       </c>
       <c r="M10">
-        <v>117940</v>
-      </c>
-      <c r="N10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>207831</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="3">
         <v>46203</v>
       </c>
@@ -1046,34 +979,31 @@
       <c r="F11">
         <v>26.77</v>
       </c>
-      <c r="G11" t="s">
-        <v>24</v>
+      <c r="G11" s="1">
+        <v>0.65</v>
       </c>
       <c r="H11">
-        <v>0.65</v>
+        <v>17.4</v>
       </c>
       <c r="I11" s="1">
-        <v>17.4</v>
+        <v>0.66</v>
       </c>
       <c r="J11">
-        <v>0.66</v>
-      </c>
-      <c r="K11" s="1">
         <v>17.67</v>
       </c>
-      <c r="L11" t="s">
-        <v>34</v>
+      <c r="K11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11">
+        <v>116250</v>
       </c>
       <c r="M11">
-        <v>116250</v>
-      </c>
-      <c r="N11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>208259</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="4" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -1081,32 +1011,32 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:13">
       <c r="A15" s="5" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B16" s="7">
-        <v>228.66</v>
+        <v>228.67</v>
       </c>
       <c r="C16" s="7">
         <v>8</v>
@@ -1123,7 +1053,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B17" s="7">
         <v>64.11</v>
@@ -1143,10 +1073,10 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="9" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B18" s="10">
-        <v>292.77</v>
+        <v>292.78</v>
       </c>
       <c r="C18" s="10">
         <v>10</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="50">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,64 +55,97 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>В5786КН</t>
+  </si>
+  <si>
+    <t>В8990ВР</t>
   </si>
   <si>
     <t>В0843ТМ</t>
   </si>
   <si>
-    <t>В8990ВР</t>
-  </si>
-  <si>
-    <t>В5786КН</t>
+    <t>78970155027720741</t>
+  </si>
+  <si>
+    <t>78970155027720766</t>
   </si>
   <si>
     <t>78970155027720758</t>
   </si>
   <si>
-    <t>78970155027720766</t>
-  </si>
-  <si>
-    <t>78970155027720741</t>
+    <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>2026-07-03 11:05:05</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:06:53</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:06:54</t>
-  </si>
-  <si>
-    <t>2026-07-07 09:50:49</t>
-  </si>
-  <si>
-    <t>2026-07-08 12:14:55</t>
-  </si>
-  <si>
-    <t>2026-07-08 12:20:15</t>
-  </si>
-  <si>
-    <t>2026-07-10 12:56:17</t>
-  </si>
-  <si>
-    <t>2026-07-10 14:39:17</t>
-  </si>
-  <si>
-    <t>2026-07-13 15:34:46</t>
-  </si>
-  <si>
-    <t>2026-07-15 14:08:29</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>11:11:00</t>
+  </si>
+  <si>
+    <t>15:39:00</t>
+  </si>
+  <si>
+    <t>09:39:00</t>
+  </si>
+  <si>
+    <t>08:37:00</t>
+  </si>
+  <si>
+    <t>15:31:00</t>
+  </si>
+  <si>
+    <t>11:52:00</t>
+  </si>
+  <si>
+    <t>13:53:00</t>
+  </si>
+  <si>
+    <t>14:10:00</t>
+  </si>
+  <si>
+    <t>11:33:00</t>
+  </si>
+  <si>
+    <t>3234926980 3234926980</t>
+  </si>
+  <si>
+    <t>3234943654 3234943654</t>
+  </si>
+  <si>
+    <t>3235103498 3235103498</t>
+  </si>
+  <si>
+    <t>3235208678 3235208678</t>
+  </si>
+  <si>
+    <t>3235257385 3235257385</t>
+  </si>
+  <si>
+    <t>3235303809 3235303809</t>
+  </si>
+  <si>
+    <t>3235456896 3235456896</t>
+  </si>
+  <si>
+    <t>3235530417 3235530417</t>
+  </si>
+  <si>
+    <t>3235597109 3235597109</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА</t>
@@ -529,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -538,15 +574,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -583,478 +621,500 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46206</v>
+        <v>46220</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2">
+        <v>1.48</v>
+      </c>
+      <c r="I2" s="1">
+        <v>51.8</v>
+      </c>
+      <c r="J2">
+        <v>1.51</v>
+      </c>
+      <c r="K2" s="1">
+        <v>52.85</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2">
+        <v>308135</v>
+      </c>
+      <c r="N2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3">
+        <v>30.88</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3">
+        <v>0.63</v>
+      </c>
+      <c r="I3" s="1">
+        <v>19.45</v>
+      </c>
+      <c r="J3">
+        <v>0.64</v>
+      </c>
+      <c r="K3" s="1">
+        <v>19.76</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3">
+        <v>117180</v>
+      </c>
+      <c r="N3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46224</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4">
+        <v>27.81</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4">
+        <v>0.63</v>
+      </c>
+      <c r="I4" s="1">
+        <v>17.52</v>
+      </c>
+      <c r="J4">
+        <v>0.64</v>
+      </c>
+      <c r="K4" s="1">
+        <v>17.8</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4">
+        <v>118600</v>
+      </c>
+      <c r="N4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46226</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5">
+        <v>22</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5">
+        <v>1.51</v>
+      </c>
+      <c r="I5" s="1">
+        <v>33.22</v>
+      </c>
+      <c r="J5">
+        <v>1.54</v>
+      </c>
+      <c r="K5" s="1">
+        <v>33.88</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5">
+        <v>308270</v>
+      </c>
+      <c r="N5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6">
+        <v>21.88</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6">
+        <v>0.63</v>
+      </c>
+      <c r="I6" s="1">
+        <v>13.78</v>
+      </c>
+      <c r="J6">
+        <v>0.64</v>
+      </c>
+      <c r="K6" s="1">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="L6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6">
+        <v>117430</v>
+      </c>
+      <c r="N6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7">
+        <v>20.55</v>
+      </c>
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7">
+        <v>0.63</v>
+      </c>
+      <c r="I7" s="1">
+        <v>12.95</v>
+      </c>
+      <c r="J7">
+        <v>0.64</v>
+      </c>
+      <c r="K7" s="1">
+        <v>13.15</v>
+      </c>
+      <c r="L7" t="s">
+        <v>31</v>
+      </c>
+      <c r="M7">
+        <v>118800</v>
+      </c>
+      <c r="N7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8">
+        <v>19.03</v>
+      </c>
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8">
+        <v>0.63</v>
+      </c>
+      <c r="I8" s="1">
+        <v>11.99</v>
+      </c>
+      <c r="J8">
+        <v>0.64</v>
+      </c>
+      <c r="K8" s="1">
+        <v>12.18</v>
+      </c>
+      <c r="L8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8">
+        <v>118980</v>
+      </c>
+      <c r="N8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9">
+        <v>25.16</v>
+      </c>
+      <c r="G9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9">
+        <v>0.63</v>
+      </c>
+      <c r="I9" s="1">
+        <v>15.85</v>
+      </c>
+      <c r="J9">
+        <v>0.64</v>
+      </c>
+      <c r="K9" s="1">
+        <v>16.1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9">
+        <v>117600</v>
+      </c>
+      <c r="N9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D10" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1">
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10">
+        <v>20.01</v>
+      </c>
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10">
+        <v>1.52</v>
+      </c>
+      <c r="I10" s="1">
+        <v>30.42</v>
+      </c>
+      <c r="J10">
+        <v>1.55</v>
+      </c>
+      <c r="K10" s="1">
+        <v>31.02</v>
+      </c>
+      <c r="L10" t="s">
+        <v>34</v>
+      </c>
+      <c r="M10">
+        <v>308404</v>
+      </c>
+      <c r="N10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="7">
+        <v>145.31</v>
+      </c>
+      <c r="C15" s="7">
+        <v>6</v>
+      </c>
+      <c r="D15" s="8">
         <v>0.63</v>
       </c>
-      <c r="H2">
-        <v>12.6</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="J2">
-        <v>12.8</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2">
-        <v>118140</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="3">
-        <v>46209</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>10</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H3">
-        <v>14.7</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J3">
-        <v>15</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="E15" s="7">
+        <v>91.54000000000001</v>
+      </c>
+      <c r="F15" s="7">
+        <v>92.98999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="L3">
-        <v>116510</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="3">
-        <v>46209</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <v>31.27</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H4">
-        <v>19.39</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J4">
-        <v>19.7</v>
-      </c>
-      <c r="K4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4">
-        <v>116510</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="3">
-        <v>46210</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>34.09</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H5">
-        <v>50.11</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J5">
-        <v>51.14</v>
-      </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5">
-        <v>307719</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="3">
-        <v>46211</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.46</v>
-      </c>
-      <c r="H6">
-        <v>14.6</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="J6">
-        <v>14.9</v>
-      </c>
-      <c r="K6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6">
-        <v>118292</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="3">
-        <v>46211</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7">
-        <v>36.83</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H7">
-        <v>22.83</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J7">
-        <v>23.2</v>
-      </c>
-      <c r="K7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7">
-        <v>118292</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="3">
-        <v>46213</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8">
-        <v>30</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1.46</v>
-      </c>
-      <c r="H8">
-        <v>43.8</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="J8">
-        <v>44.7</v>
-      </c>
-      <c r="K8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L8">
-        <v>307860</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="3">
-        <v>46213</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9">
-        <v>26.68</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H9">
-        <v>16.54</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J9">
-        <v>16.81</v>
-      </c>
-      <c r="K9" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9">
-        <v>116800</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="3">
-        <v>46216</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10">
-        <v>29.11</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H10">
-        <v>18.05</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J10">
-        <v>18.34</v>
-      </c>
-      <c r="K10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10">
-        <v>118440</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="3">
-        <v>46218</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11">
-        <v>26.22</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H11">
-        <v>16.26</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J11">
-        <v>16.52</v>
-      </c>
-      <c r="K11" t="s">
-        <v>31</v>
-      </c>
-      <c r="L11">
-        <v>117000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="5" t="s">
+      <c r="B16" s="7">
+        <v>77.01000000000001</v>
+      </c>
+      <c r="C16" s="7">
+        <v>3</v>
+      </c>
+      <c r="D16" s="8">
+        <v>1.499</v>
+      </c>
+      <c r="E16" s="7">
+        <v>115.44</v>
+      </c>
+      <c r="F16" s="7">
+        <v>117.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="10">
+        <v>222.32</v>
+      </c>
+      <c r="C17" s="10">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="7">
-        <v>170.11</v>
-      </c>
-      <c r="C16" s="7">
-        <v>6</v>
-      </c>
-      <c r="D16" s="8">
-        <v>0.6212</v>
-      </c>
-      <c r="E16" s="7">
-        <v>105.67</v>
-      </c>
-      <c r="F16" s="7">
-        <v>107.37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="7">
-        <v>84.09</v>
-      </c>
-      <c r="C17" s="7">
-        <v>4</v>
-      </c>
-      <c r="D17" s="8">
-        <v>1.4652</v>
-      </c>
-      <c r="E17" s="7">
-        <v>123.21</v>
-      </c>
-      <c r="F17" s="7">
-        <v>125.74</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="10">
-        <v>254.2</v>
-      </c>
-      <c r="C18" s="10">
-        <v>10</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="10">
-        <v>228.88</v>
-      </c>
-      <c r="F18" s="10">
-        <v>233.11</v>
+      <c r="D17" s="8"/>
+      <c r="E17" s="10">
+        <v>206.98</v>
+      </c>
+      <c r="F17" s="10">
+        <v>210.74</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A13:F13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
@@ -173,7 +173,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1065,7 +1065,7 @@
         <v>6</v>
       </c>
       <c r="D15" s="8">
-        <v>0.63</v>
+        <v>0.629964</v>
       </c>
       <c r="E15" s="7">
         <v>91.54000000000001</v>
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="8">
-        <v>1.499</v>
+        <v>1.499026</v>
       </c>
       <c r="E16" s="7">
         <v>115.44</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="51">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -565,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -578,13 +581,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -627,406 +630,436 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46220</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2">
         <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2">
+        <v>1.369</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.48</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>51.8</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>1.51</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>52.85</v>
       </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2">
         <v>308135</v>
       </c>
-      <c r="N2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46220</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>30.88</v>
+        <v>30.875</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
         <v>0.63</v>
       </c>
-      <c r="I3" s="1">
-        <v>19.45</v>
-      </c>
       <c r="J3">
+        <v>19.45125</v>
+      </c>
+      <c r="K3" s="1">
         <v>0.64</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>19.76</v>
       </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3">
+      <c r="M3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3">
         <v>117180</v>
       </c>
-      <c r="N3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46224</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>27.81</v>
+        <v>27.813</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
         <v>0.63</v>
       </c>
-      <c r="I4" s="1">
-        <v>17.52</v>
-      </c>
       <c r="J4">
+        <v>17.52219</v>
+      </c>
+      <c r="K4" s="1">
         <v>0.64</v>
       </c>
-      <c r="K4" s="1">
-        <v>17.8</v>
-      </c>
-      <c r="L4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>17.80032</v>
+      </c>
+      <c r="M4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4">
         <v>118600</v>
       </c>
-      <c r="N4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46226</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5">
         <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5">
+        <v>1.401</v>
+      </c>
+      <c r="I5" s="1">
         <v>1.51</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>33.22</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>1.54</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>33.88</v>
       </c>
-      <c r="L5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5">
+      <c r="M5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5">
         <v>308270</v>
       </c>
-      <c r="N5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3">
         <v>46227</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>21.88</v>
+        <v>21.875</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
         <v>0.63</v>
       </c>
-      <c r="I6" s="1">
-        <v>13.78</v>
-      </c>
       <c r="J6">
+        <v>13.78125</v>
+      </c>
+      <c r="K6" s="1">
         <v>0.64</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>14</v>
       </c>
-      <c r="L6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6">
+      <c r="M6" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6">
         <v>117430</v>
       </c>
-      <c r="N6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3">
         <v>46227</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>20.55</v>
+        <v>20.547</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
         <v>0.63</v>
       </c>
-      <c r="I7" s="1">
-        <v>12.95</v>
-      </c>
       <c r="J7">
+        <v>12.94461</v>
+      </c>
+      <c r="K7" s="1">
         <v>0.64</v>
       </c>
-      <c r="K7" s="1">
-        <v>13.15</v>
-      </c>
-      <c r="L7" t="s">
-        <v>31</v>
-      </c>
-      <c r="M7">
+      <c r="L7" s="1">
+        <v>13.15008</v>
+      </c>
+      <c r="M7" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7">
         <v>118800</v>
       </c>
-      <c r="N7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3">
         <v>46231</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>19.03</v>
+        <v>19.031</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
         <v>0.63</v>
       </c>
-      <c r="I8" s="1">
-        <v>11.99</v>
-      </c>
       <c r="J8">
+        <v>11.98953</v>
+      </c>
+      <c r="K8" s="1">
         <v>0.64</v>
       </c>
-      <c r="K8" s="1">
-        <v>12.18</v>
-      </c>
-      <c r="L8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8">
+      <c r="L8" s="1">
+        <v>12.17984</v>
+      </c>
+      <c r="M8" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8">
         <v>118980</v>
       </c>
-      <c r="N8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3">
         <v>46232</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>25.16</v>
+        <v>25.156</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
         <v>0.63</v>
       </c>
-      <c r="I9" s="1">
-        <v>15.85</v>
-      </c>
       <c r="J9">
+        <v>15.84828</v>
+      </c>
+      <c r="K9" s="1">
         <v>0.64</v>
       </c>
-      <c r="K9" s="1">
-        <v>16.1</v>
-      </c>
-      <c r="L9" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9">
+      <c r="L9" s="1">
+        <v>16.09984</v>
+      </c>
+      <c r="M9" t="s">
+        <v>34</v>
+      </c>
+      <c r="N9">
         <v>117600</v>
       </c>
-      <c r="N9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="3">
         <v>46233</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>20.01</v>
+        <v>20.013</v>
       </c>
       <c r="G10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H10">
+        <v>1.449</v>
+      </c>
+      <c r="I10" s="1">
         <v>1.52</v>
       </c>
-      <c r="I10" s="1">
-        <v>30.42</v>
-      </c>
       <c r="J10">
+        <v>30.41976</v>
+      </c>
+      <c r="K10" s="1">
         <v>1.55</v>
       </c>
-      <c r="K10" s="1">
-        <v>31.02</v>
-      </c>
-      <c r="L10" t="s">
-        <v>34</v>
-      </c>
-      <c r="M10">
+      <c r="L10" s="1">
+        <v>31.02015</v>
+      </c>
+      <c r="M10" t="s">
+        <v>35</v>
+      </c>
+      <c r="N10">
         <v>308404</v>
       </c>
-      <c r="N10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1034,38 +1067,38 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:15">
       <c r="A14" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="7">
-        <v>145.31</v>
+        <v>145.297</v>
       </c>
       <c r="C15" s="7">
         <v>6</v>
       </c>
       <c r="D15" s="8">
-        <v>0.629964</v>
+        <v>0.63</v>
       </c>
       <c r="E15" s="7">
         <v>91.54000000000001</v>
@@ -1074,18 +1107,18 @@
         <v>92.98999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:15">
       <c r="A16" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="7">
-        <v>77.01000000000001</v>
+        <v>77.01300000000001</v>
       </c>
       <c r="C16" s="7">
         <v>3</v>
       </c>
       <c r="D16" s="8">
-        <v>1.499026</v>
+        <v>1.498965</v>
       </c>
       <c r="E16" s="7">
         <v>115.44</v>
@@ -1096,10 +1129,10 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" s="10">
-        <v>222.32</v>
+        <v>222.31</v>
       </c>
       <c r="C17" s="10">
         <v>9</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="50">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -174,9 +171,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -270,10 +267,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -568,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -581,13 +578,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -630,436 +627,406 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46220</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>35</v>
       </c>
       <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2">
+        <v>1.48</v>
+      </c>
+      <c r="I2" s="1">
+        <v>51.8</v>
+      </c>
+      <c r="J2">
+        <v>1.51</v>
+      </c>
+      <c r="K2" s="1">
+        <v>52.85</v>
+      </c>
+      <c r="L2" t="s">
         <v>26</v>
       </c>
-      <c r="H2">
-        <v>1.369</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="J2">
-        <v>51.8</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L2" s="1">
-        <v>52.85</v>
-      </c>
-      <c r="M2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>308135</v>
       </c>
-      <c r="O2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46220</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3">
         <v>30.875</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I3" s="1">
-        <v>0.63</v>
+        <v>19.451</v>
       </c>
       <c r="J3">
-        <v>19.45125</v>
+        <v>0.64</v>
       </c>
       <c r="K3" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L3" s="1">
         <v>19.76</v>
       </c>
-      <c r="M3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3">
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3">
         <v>117180</v>
       </c>
-      <c r="O3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46224</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F4">
         <v>27.813</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I4" s="1">
-        <v>0.63</v>
+        <v>17.522</v>
       </c>
       <c r="J4">
-        <v>17.52219</v>
+        <v>0.64</v>
       </c>
       <c r="K4" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L4" s="1">
-        <v>17.80032</v>
-      </c>
-      <c r="M4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4">
+        <v>17.8</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4">
         <v>118600</v>
       </c>
-      <c r="O4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46226</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5">
         <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H5">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I5" s="1">
-        <v>1.51</v>
+        <v>33.22</v>
       </c>
       <c r="J5">
-        <v>33.22</v>
+        <v>1.54</v>
       </c>
       <c r="K5" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L5" s="1">
         <v>33.88</v>
       </c>
-      <c r="M5" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5">
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5">
         <v>308270</v>
       </c>
-      <c r="O5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46227</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6">
         <v>21.875</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I6" s="1">
-        <v>0.63</v>
+        <v>13.781</v>
       </c>
       <c r="J6">
-        <v>13.78125</v>
+        <v>0.64</v>
       </c>
       <c r="K6" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L6" s="1">
         <v>14</v>
       </c>
-      <c r="M6" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6">
+      <c r="L6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6">
         <v>117430</v>
       </c>
-      <c r="O6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46227</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F7">
         <v>20.547</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I7" s="1">
-        <v>0.63</v>
+        <v>12.945</v>
       </c>
       <c r="J7">
-        <v>12.94461</v>
+        <v>0.64</v>
       </c>
       <c r="K7" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L7" s="1">
-        <v>13.15008</v>
-      </c>
-      <c r="M7" t="s">
-        <v>32</v>
-      </c>
-      <c r="N7">
+        <v>13.15</v>
+      </c>
+      <c r="L7" t="s">
+        <v>31</v>
+      </c>
+      <c r="M7">
         <v>118800</v>
       </c>
-      <c r="O7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46231</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F8">
         <v>19.031</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I8" s="1">
-        <v>0.63</v>
+        <v>11.99</v>
       </c>
       <c r="J8">
-        <v>11.98953</v>
+        <v>0.64</v>
       </c>
       <c r="K8" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L8" s="1">
-        <v>12.17984</v>
-      </c>
-      <c r="M8" t="s">
-        <v>33</v>
-      </c>
-      <c r="N8">
+        <v>12.18</v>
+      </c>
+      <c r="L8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8">
         <v>118980</v>
       </c>
-      <c r="O8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46232</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9">
         <v>25.156</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I9" s="1">
-        <v>0.63</v>
+        <v>15.848</v>
       </c>
       <c r="J9">
-        <v>15.84828</v>
+        <v>0.64</v>
       </c>
       <c r="K9" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L9" s="1">
-        <v>16.09984</v>
-      </c>
-      <c r="M9" t="s">
-        <v>34</v>
-      </c>
-      <c r="N9">
+        <v>16.1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9">
         <v>117600</v>
       </c>
-      <c r="O9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46233</v>
       </c>
       <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10">
         <v>20.013</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H10">
-        <v>1.449</v>
+        <v>1.52</v>
       </c>
       <c r="I10" s="1">
-        <v>1.52</v>
+        <v>30.42</v>
       </c>
       <c r="J10">
-        <v>30.41976</v>
+        <v>1.55</v>
       </c>
       <c r="K10" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L10" s="1">
-        <v>31.02015</v>
-      </c>
-      <c r="M10" t="s">
-        <v>35</v>
-      </c>
-      <c r="N10">
+        <v>31.02</v>
+      </c>
+      <c r="L10" t="s">
+        <v>34</v>
+      </c>
+      <c r="M10">
         <v>308404</v>
       </c>
-      <c r="O10" t="s">
+      <c r="N10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="4" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1067,69 +1034,69 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:14">
       <c r="A14" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="E14" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" s="7">
         <v>145.297</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="8">
         <v>6</v>
       </c>
       <c r="D15" s="8">
         <v>0.63</v>
       </c>
-      <c r="E15" s="7">
-        <v>91.54000000000001</v>
-      </c>
-      <c r="F15" s="7">
+      <c r="E15" s="8">
+        <v>91.53700000000001</v>
+      </c>
+      <c r="F15" s="8">
         <v>92.98999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:14">
       <c r="A16" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="7">
         <v>77.01300000000001</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="8">
         <v>3</v>
       </c>
       <c r="D16" s="8">
-        <v>1.498965</v>
-      </c>
-      <c r="E16" s="7">
+        <v>1.499</v>
+      </c>
+      <c r="E16" s="8">
         <v>115.44</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="8">
         <v>117.75</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" s="10">
         <v>222.31</v>
@@ -1139,7 +1106,7 @@
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="10">
-        <v>206.98</v>
+        <v>206.977</v>
       </c>
       <c r="F17" s="10">
         <v>210.74</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="37">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,94 +55,58 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
+    <t>Варна Варненчик</t>
+  </si>
+  <si>
+    <t>Варна Цар Освободител</t>
+  </si>
+  <si>
+    <t>В0843ТМ</t>
+  </si>
+  <si>
+    <t>В8990ВР</t>
   </si>
   <si>
     <t>В5786КН</t>
   </si>
   <si>
-    <t>В8990ВР</t>
-  </si>
-  <si>
-    <t>В0843ТМ</t>
+    <t>78970155027720758</t>
+  </si>
+  <si>
+    <t>78970155027720766</t>
   </si>
   <si>
     <t>78970155027720741</t>
   </si>
   <si>
-    <t>78970155027720766</t>
-  </si>
-  <si>
-    <t>78970155027720758</t>
+    <t>E GAS LPG</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>11:11:00</t>
-  </si>
-  <si>
-    <t>15:39:00</t>
-  </si>
-  <si>
-    <t>09:39:00</t>
-  </si>
-  <si>
-    <t>08:37:00</t>
-  </si>
-  <si>
-    <t>15:31:00</t>
-  </si>
-  <si>
-    <t>11:52:00</t>
-  </si>
-  <si>
-    <t>13:53:00</t>
-  </si>
-  <si>
-    <t>14:10:00</t>
-  </si>
-  <si>
-    <t>11:33:00</t>
-  </si>
-  <si>
-    <t>3234926980 3234926980</t>
-  </si>
-  <si>
-    <t>3234943654 3234943654</t>
-  </si>
-  <si>
-    <t>3235103498 3235103498</t>
-  </si>
-  <si>
-    <t>3235208678 3235208678</t>
-  </si>
-  <si>
-    <t>3235257385 3235257385</t>
-  </si>
-  <si>
-    <t>3235303809 3235303809</t>
-  </si>
-  <si>
-    <t>3235456896 3235456896</t>
-  </si>
-  <si>
-    <t>3235530417 3235530417</t>
-  </si>
-  <si>
-    <t>3235597109 3235597109</t>
+    <t>10:19</t>
+  </si>
+  <si>
+    <t>14:22</t>
+  </si>
+  <si>
+    <t>09:33</t>
+  </si>
+  <si>
+    <t>15:23</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>10:22</t>
+  </si>
+  <si>
+    <t>14:36</t>
+  </si>
+  <si>
+    <t>11:35</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА</t>
@@ -171,9 +132,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -267,10 +228,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -565,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -574,17 +535,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -624,409 +584,379 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46220</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>29.215</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="H2">
+        <v>18.698</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="J2">
+        <v>18.99</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2">
+        <v>119170</v>
+      </c>
+      <c r="M2">
+        <v>229138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H3">
+        <v>15.2</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J3">
+        <v>15.5</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3">
+        <v>58142</v>
+      </c>
+      <c r="M3">
+        <v>134581</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4">
+        <v>37.076</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H4">
+        <v>24.099</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J4">
+        <v>24.47</v>
+      </c>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4">
+        <v>117840</v>
+      </c>
+      <c r="M4">
+        <v>134581</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="3">
+        <v>46241</v>
+      </c>
+      <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>37.53</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H5">
+        <v>24.394</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J5">
+        <v>24.77</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5">
+        <v>231798</v>
+      </c>
+      <c r="M5">
+        <v>290153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="3">
+        <v>46244</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H6">
+        <v>15.2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J6">
+        <v>15.5</v>
+      </c>
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>137007</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="3">
+        <v>46244</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7">
+        <v>13.758</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H7">
+        <v>8.943</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J7">
+        <v>9.08</v>
+      </c>
+      <c r="K7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7">
+        <v>119450</v>
+      </c>
+      <c r="M7">
+        <v>137009</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="3">
+        <v>46245</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2">
-        <v>35</v>
-      </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2">
-        <v>1.48</v>
-      </c>
-      <c r="I2" s="1">
-        <v>51.8</v>
-      </c>
-      <c r="J2">
-        <v>1.51</v>
-      </c>
-      <c r="K2" s="1">
-        <v>52.85</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2">
-        <v>308135</v>
-      </c>
-      <c r="N2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46220</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8">
+        <v>30.013</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H8">
+        <v>45.62</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J8">
+        <v>46.52</v>
+      </c>
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8">
+        <v>308600</v>
+      </c>
+      <c r="M8">
+        <v>291588</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="3">
+        <v>46245</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
         <v>21</v>
       </c>
-      <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3">
-        <v>30.875</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3">
-        <v>0.63</v>
-      </c>
-      <c r="I3" s="1">
-        <v>19.451</v>
-      </c>
-      <c r="J3">
-        <v>0.64</v>
-      </c>
-      <c r="K3" s="1">
-        <v>19.76</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3">
-        <v>117180</v>
-      </c>
-      <c r="N3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46224</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="F9">
+        <v>32.136</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H9">
+        <v>20.888</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J9">
+        <v>21.21</v>
+      </c>
+      <c r="K9" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9">
+        <v>118150</v>
+      </c>
+      <c r="M9">
+        <v>291681</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4">
-        <v>27.813</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4">
-        <v>0.63</v>
-      </c>
-      <c r="I4" s="1">
-        <v>17.522</v>
-      </c>
-      <c r="J4">
-        <v>0.64</v>
-      </c>
-      <c r="K4" s="1">
-        <v>17.8</v>
-      </c>
-      <c r="L4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4">
-        <v>118600</v>
-      </c>
-      <c r="N4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46226</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5">
-        <v>1.51</v>
-      </c>
-      <c r="I5" s="1">
-        <v>33.22</v>
-      </c>
-      <c r="J5">
-        <v>1.54</v>
-      </c>
-      <c r="K5" s="1">
-        <v>33.88</v>
-      </c>
-      <c r="L5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5">
-        <v>308270</v>
-      </c>
-      <c r="N5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="3">
-        <v>46227</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E10" t="s">
         <v>21</v>
       </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6">
-        <v>21.875</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6">
-        <v>0.63</v>
-      </c>
-      <c r="I6" s="1">
-        <v>13.781</v>
-      </c>
-      <c r="J6">
-        <v>0.64</v>
-      </c>
-      <c r="K6" s="1">
-        <v>14</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="F10">
+        <v>16.727</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H10">
+        <v>10.873</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J10">
+        <v>11.04</v>
+      </c>
+      <c r="K10" t="s">
         <v>30</v>
       </c>
-      <c r="M6">
-        <v>117430</v>
-      </c>
-      <c r="N6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="3">
-        <v>46227</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7">
-        <v>20.547</v>
-      </c>
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7">
-        <v>0.63</v>
-      </c>
-      <c r="I7" s="1">
-        <v>12.945</v>
-      </c>
-      <c r="J7">
-        <v>0.64</v>
-      </c>
-      <c r="K7" s="1">
-        <v>13.15</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="L10">
+        <v>118260</v>
+      </c>
+      <c r="M10">
+        <v>292489</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="M7">
-        <v>118800</v>
-      </c>
-      <c r="N7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="3">
-        <v>46231</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8">
-        <v>19.031</v>
-      </c>
-      <c r="G8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8">
-        <v>0.63</v>
-      </c>
-      <c r="I8" s="1">
-        <v>11.99</v>
-      </c>
-      <c r="J8">
-        <v>0.64</v>
-      </c>
-      <c r="K8" s="1">
-        <v>12.18</v>
-      </c>
-      <c r="L8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8">
-        <v>118980</v>
-      </c>
-      <c r="N8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="3">
-        <v>46232</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9">
-        <v>25.156</v>
-      </c>
-      <c r="G9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9">
-        <v>0.63</v>
-      </c>
-      <c r="I9" s="1">
-        <v>15.848</v>
-      </c>
-      <c r="J9">
-        <v>0.64</v>
-      </c>
-      <c r="K9" s="1">
-        <v>16.1</v>
-      </c>
-      <c r="L9" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9">
-        <v>117600</v>
-      </c>
-      <c r="N9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="3">
-        <v>46233</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10">
-        <v>20.013</v>
-      </c>
-      <c r="G10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10">
-        <v>1.52</v>
-      </c>
-      <c r="I10" s="1">
-        <v>30.42</v>
-      </c>
-      <c r="J10">
-        <v>1.55</v>
-      </c>
-      <c r="K10" s="1">
-        <v>31.02</v>
-      </c>
-      <c r="L10" t="s">
-        <v>34</v>
-      </c>
-      <c r="M10">
-        <v>308404</v>
-      </c>
-      <c r="N10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1034,82 +964,82 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:13">
       <c r="A14" s="5" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B15" s="7">
-        <v>145.297</v>
-      </c>
-      <c r="C15" s="8">
+        <v>166.442</v>
+      </c>
+      <c r="C15" s="7">
         <v>6</v>
       </c>
       <c r="D15" s="8">
-        <v>0.63</v>
-      </c>
-      <c r="E15" s="8">
-        <v>91.53700000000001</v>
-      </c>
-      <c r="F15" s="8">
-        <v>92.98999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>0.64824</v>
+      </c>
+      <c r="E15" s="7">
+        <v>107.9</v>
+      </c>
+      <c r="F15" s="7">
+        <v>109.56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="7">
-        <v>77.01300000000001</v>
-      </c>
-      <c r="C16" s="8">
+        <v>50.013</v>
+      </c>
+      <c r="C16" s="7">
         <v>3</v>
       </c>
       <c r="D16" s="8">
-        <v>1.499</v>
-      </c>
-      <c r="E16" s="8">
-        <v>115.44</v>
-      </c>
-      <c r="F16" s="8">
-        <v>117.75</v>
+        <v>1.52</v>
+      </c>
+      <c r="E16" s="7">
+        <v>76.02</v>
+      </c>
+      <c r="F16" s="7">
+        <v>77.52</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="9" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B17" s="10">
-        <v>222.31</v>
+        <v>216.455</v>
       </c>
       <c r="C17" s="10">
         <v>9</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="10">
-        <v>206.977</v>
+        <v>183.92</v>
       </c>
       <c r="F17" s="10">
-        <v>210.74</v>
+        <v>187.08</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,10 +58,10 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна Цар Освободител</t>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
   </si>
   <si>
     <t>В0843ТМ</t>
@@ -85,28 +88,52 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>10:19</t>
-  </si>
-  <si>
-    <t>14:22</t>
-  </si>
-  <si>
-    <t>09:33</t>
-  </si>
-  <si>
-    <t>15:23</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>10:22</t>
-  </si>
-  <si>
-    <t>14:36</t>
-  </si>
-  <si>
-    <t>11:35</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>10:20:00</t>
+  </si>
+  <si>
+    <t>10:28:00</t>
+  </si>
+  <si>
+    <t>14:58:00</t>
+  </si>
+  <si>
+    <t>12:53:00</t>
+  </si>
+  <si>
+    <t>14:04:00</t>
+  </si>
+  <si>
+    <t>14:03:00</t>
+  </si>
+  <si>
+    <t>09:57:00</t>
+  </si>
+  <si>
+    <t>3236510485 3236510485</t>
+  </si>
+  <si>
+    <t>3236654568 3236654568</t>
+  </si>
+  <si>
+    <t>3236715898 3236715898</t>
+  </si>
+  <si>
+    <t>3236922666 3236922666</t>
+  </si>
+  <si>
+    <t>3236958600 3236958600</t>
+  </si>
+  <si>
+    <t>3237059295 3237059295</t>
+  </si>
+  <si>
+    <t>3237205336 3237205336</t>
+  </si>
+  <si>
+    <t>3237217946 3237217946</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА</t>
@@ -131,10 +158,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -214,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -228,10 +256,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -526,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -535,16 +565,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -584,95 +615,104 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2">
+        <v>37.38</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I2" s="1">
+        <v>37.006</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K2" s="1">
+        <v>24.671</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2">
+        <v>119710</v>
+      </c>
+      <c r="N2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2">
-        <v>29.215</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="H2">
-        <v>18.698</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="J2">
-        <v>18.99</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2">
-        <v>119170</v>
-      </c>
-      <c r="M2">
-        <v>229138</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46238</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
         <v>22</v>
       </c>
       <c r="F3">
-        <v>10</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H3">
-        <v>15.2</v>
+        <v>34.91</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.99</v>
       </c>
       <c r="I3" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J3">
-        <v>15.5</v>
-      </c>
-      <c r="K3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3">
-        <v>58142</v>
+        <v>34.561</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K3" s="1">
+        <v>23.041</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
       </c>
       <c r="M3">
-        <v>134581</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>118500</v>
+      </c>
+      <c r="N3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
-        <v>46238</v>
+        <v>46255</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
@@ -681,162 +721,174 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>37.076</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H4">
-        <v>24.099</v>
+        <v>36.48</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.99</v>
       </c>
       <c r="I4" s="1">
+        <v>36.115</v>
+      </c>
+      <c r="J4" s="1">
         <v>0.66</v>
       </c>
-      <c r="J4">
-        <v>24.47</v>
-      </c>
-      <c r="K4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4">
-        <v>117840</v>
+      <c r="K4" s="1">
+        <v>24.077</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
       </c>
       <c r="M4">
-        <v>134581</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>119960</v>
+      </c>
+      <c r="N4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
-        <v>46241</v>
+        <v>46259</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1.459</v>
+      </c>
+      <c r="I5" s="1">
+        <v>43.77</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="K5" s="1">
+        <v>47.4</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5">
+        <v>308945</v>
+      </c>
+      <c r="N5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>37.53</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H5">
-        <v>24.394</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J5">
-        <v>24.77</v>
-      </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5">
-        <v>231798</v>
-      </c>
-      <c r="M5">
-        <v>290153</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="3">
-        <v>46244</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
         <v>22</v>
       </c>
       <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H6">
-        <v>15.2</v>
+        <v>31.56</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.99</v>
       </c>
       <c r="I6" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J6">
-        <v>15.5</v>
-      </c>
-      <c r="K6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
+        <v>31.244</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K6" s="1">
+        <v>20.83</v>
+      </c>
+      <c r="L6" t="s">
+        <v>28</v>
       </c>
       <c r="M6">
-        <v>137007</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>118720</v>
+      </c>
+      <c r="N6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
-        <v>46244</v>
+        <v>46262</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>37.39</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I7" s="1">
+        <v>37.016</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K7" s="1">
+        <v>24.677</v>
+      </c>
+      <c r="L7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7">
+        <v>120230</v>
+      </c>
+      <c r="N7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="3">
+        <v>46265</v>
+      </c>
+      <c r="B8" t="s">
         <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7">
-        <v>13.758</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H7">
-        <v>8.943</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J7">
-        <v>9.08</v>
-      </c>
-      <c r="K7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7">
-        <v>119450</v>
-      </c>
-      <c r="M7">
-        <v>137009</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="3">
-        <v>46245</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -848,203 +900,168 @@
         <v>22</v>
       </c>
       <c r="F8">
-        <v>30.013</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H8">
-        <v>45.62</v>
+        <v>15.71</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0.99</v>
       </c>
       <c r="I8" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J8">
-        <v>46.52</v>
-      </c>
-      <c r="K8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L8">
-        <v>308600</v>
+        <v>15.553</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K8" s="1">
+        <v>10.369</v>
+      </c>
+      <c r="L8" t="s">
+        <v>30</v>
       </c>
       <c r="M8">
-        <v>291588</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>118880</v>
+      </c>
+      <c r="N8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
-        <v>46245</v>
+        <v>46265</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>32.136</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H9">
-        <v>20.888</v>
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1.459</v>
       </c>
       <c r="I9" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J9">
-        <v>21.21</v>
-      </c>
-      <c r="K9" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9">
-        <v>118150</v>
+        <v>43.77</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="K9" s="1">
+        <v>48.3</v>
+      </c>
+      <c r="L9" t="s">
+        <v>31</v>
       </c>
       <c r="M9">
-        <v>291681</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="3">
-        <v>46248</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10">
-        <v>16.727</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H10">
-        <v>10.873</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J10">
-        <v>11.04</v>
-      </c>
-      <c r="K10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10">
-        <v>118260</v>
-      </c>
-      <c r="M10">
-        <v>292489</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>309222</v>
+      </c>
+      <c r="N9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="7">
+        <v>193.43</v>
+      </c>
+      <c r="C14" s="8">
+        <v>6</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0.99</v>
+      </c>
+      <c r="E14" s="7">
+        <v>191.5</v>
+      </c>
+      <c r="F14" s="7">
+        <v>127.66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B15" s="7">
-        <v>166.442</v>
-      </c>
-      <c r="C15" s="7">
-        <v>6</v>
-      </c>
-      <c r="D15" s="8">
-        <v>0.64824</v>
+        <v>60</v>
+      </c>
+      <c r="C15" s="8">
+        <v>2</v>
+      </c>
+      <c r="D15" s="9">
+        <v>1.459</v>
       </c>
       <c r="E15" s="7">
-        <v>107.9</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="F15" s="7">
-        <v>109.56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="7">
-        <v>50.013</v>
-      </c>
-      <c r="C16" s="7">
-        <v>3</v>
-      </c>
-      <c r="D16" s="8">
-        <v>1.52</v>
-      </c>
-      <c r="E16" s="7">
-        <v>76.02</v>
-      </c>
-      <c r="F16" s="7">
-        <v>77.52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="10">
-        <v>216.455</v>
-      </c>
-      <c r="C17" s="10">
-        <v>9</v>
-      </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="10">
-        <v>183.92</v>
-      </c>
-      <c r="F17" s="10">
-        <v>187.08</v>
+        <v>95.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="11">
+        <v>253.43</v>
+      </c>
+      <c r="C16" s="12">
+        <v>8</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="11">
+        <v>279.04</v>
+      </c>
+      <c r="F16" s="11">
+        <v>223.36</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА/РАЙОН ВЛАДИСЛАВ ВАРНЕНЧИК - ОБЩИНА ВАРНА.xlsx
@@ -642,10 +642,10 @@
         <v>24</v>
       </c>
       <c r="H2" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I2" s="1">
-        <v>37.006</v>
+        <v>24.297</v>
       </c>
       <c r="J2" s="1">
         <v>0.66</v>
@@ -686,10 +686,10 @@
         <v>24</v>
       </c>
       <c r="H3" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I3" s="1">
-        <v>34.561</v>
+        <v>22.691</v>
       </c>
       <c r="J3" s="1">
         <v>0.66</v>
@@ -730,10 +730,10 @@
         <v>24</v>
       </c>
       <c r="H4" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I4" s="1">
-        <v>36.115</v>
+        <v>23.712</v>
       </c>
       <c r="J4" s="1">
         <v>0.66</v>
@@ -774,10 +774,10 @@
         <v>24</v>
       </c>
       <c r="H5" s="1">
-        <v>1.459</v>
+        <v>1.55</v>
       </c>
       <c r="I5" s="1">
-        <v>43.77</v>
+        <v>46.5</v>
       </c>
       <c r="J5" s="1">
         <v>1.58</v>
@@ -818,10 +818,10 @@
         <v>24</v>
       </c>
       <c r="H6" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I6" s="1">
-        <v>31.244</v>
+        <v>20.514</v>
       </c>
       <c r="J6" s="1">
         <v>0.66</v>
@@ -862,10 +862,10 @@
         <v>24</v>
       </c>
       <c r="H7" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I7" s="1">
-        <v>37.016</v>
+        <v>24.304</v>
       </c>
       <c r="J7" s="1">
         <v>0.66</v>
@@ -906,10 +906,10 @@
         <v>24</v>
       </c>
       <c r="H8" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I8" s="1">
-        <v>15.553</v>
+        <v>10.212</v>
       </c>
       <c r="J8" s="1">
         <v>0.66</v>
@@ -950,10 +950,10 @@
         <v>24</v>
       </c>
       <c r="H9" s="1">
-        <v>1.459</v>
+        <v>1.58</v>
       </c>
       <c r="I9" s="1">
-        <v>43.77</v>
+        <v>47.4</v>
       </c>
       <c r="J9" s="1">
         <v>1.61</v>
@@ -1012,10 +1012,10 @@
         <v>6</v>
       </c>
       <c r="D14" s="9">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="E14" s="7">
-        <v>191.5</v>
+        <v>125.73</v>
       </c>
       <c r="F14" s="7">
         <v>127.66</v>
@@ -1032,10 +1032,10 @@
         <v>2</v>
       </c>
       <c r="D15" s="9">
-        <v>1.459</v>
+        <v>1.565</v>
       </c>
       <c r="E15" s="7">
-        <v>87.54000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F15" s="7">
         <v>95.7</v>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="11">
-        <v>279.04</v>
+        <v>219.63</v>
       </c>
       <c r="F16" s="11">
         <v>223.36</v>
